--- a/assets/docs/lop5/Hoat dong trai nghiem - Lop 5.xlsx
+++ b/assets/docs/lop5/Hoat dong trai nghiem - Lop 5.xlsx
@@ -2852,7 +2852,7 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 2.5 CB2a: HS chỉ ra được lời nhắn nào là tôn trọng, lời nhắn nào là trêu chọc, xúc phạm và chọn được cách trả lời phù hợp.
+          <t>Năng lực số 1.3 CB2a: HS nhập và đọc số liệu thi đua trên bảng theo dõi, nhận xét dựa trên số liệu.
 KNS: KN ứng phó với tình huống nguy hiểm và tìm kiếm sự trợ giúp.</t>
         </is>
       </c>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.3 CB2a: HS nhập và đọc số liệu thi đua trên bảng theo dõi, nhận xét dựa trên số liệu.
+          <t>Năng lực số 2.5 CB2a: HS chỉ ra được lời nhắn nào là tôn trọng, lời nhắn nào là trêu chọc, xúc phạm và chọn được cách trả lời phù hợp.
 KNS: KN ứng phó với tình huống nguy hiểm và tìm kiếm sự trợ giúp.</t>
         </is>
       </c>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.3 CB2a: HS nhập và đọc số liệu thi đua trên bảng theo dõi, nhận xét dựa trên số liệu.
+          <t>Năng lực số 1.3 CB2a: HS nhận biết cách ghi lại, sắp xếp số liệu khảo sát môi trường (lượng rác, cây xanh…) một cách đơn giản trên bảng số.
 QPAN: Tổ chức tham quan di tích lịch sử, nhà truyền thống ở địa phương hoặc xem tư liệu thay thế; giáo dục ý thức bảo vệ chủ quyền biển, đảo; trách nhiệm công dân trong xây dựng và bảo vệ Tổ quốc.</t>
         </is>
       </c>

--- a/assets/docs/lop5/Hoat dong trai nghiem - Lop 5.xlsx
+++ b/assets/docs/lop5/Hoat dong trai nghiem - Lop 5.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: EM LỚN LÊN MỖI NGÀY</t>
+          <t>Chủ đề: Em lớn lên mỗi ngày</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: EM LỚN LÊN MỖI NGÀY</t>
+          <t>Chủ đề: Em lớn lên mỗi ngày</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
@@ -603,7 +603,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: EM LỚN LÊN MỖI NGÀY</t>
+          <t>Chủ đề: Em lớn lên mỗi ngày</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
@@ -638,7 +638,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: EM LỚN LÊN MỖI NGÀY</t>
+          <t>Chủ đề: Em lớn lên mỗi ngày</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: EM LỚN LÊN MỖI NGÀY</t>
+          <t>Chủ đề: Em lớn lên mỗi ngày</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -706,7 +706,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: EM LỚN LÊN MỖI NGÀY</t>
+          <t>Chủ đề: Em lớn lên mỗi ngày</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
@@ -741,7 +741,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: EM LỚN LÊN MỖI NGÀY</t>
+          <t>Chủ đề: Em lớn lên mỗi ngày</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -775,7 +775,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: EM LỚN LÊN MỖI NGÀY</t>
+          <t>Chủ đề: Em lớn lên mỗi ngày</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -810,7 +810,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: EM LỚN LÊN MỖI NGÀY</t>
+          <t>Chủ đề: Em lớn lên mỗi ngày</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
@@ -845,7 +845,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: EM LỚN LÊN MỖI NGÀY</t>
+          <t>Chủ đề: Em lớn lên mỗi ngày</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -879,7 +879,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: EM LỚN LÊN MỖI NGÀY</t>
+          <t>Chủ đề: Em lớn lên mỗi ngày</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -914,7 +914,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: EM LỚN LÊN MỖI NGÀY</t>
+          <t>Chủ đề: Em lớn lên mỗi ngày</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
@@ -949,7 +949,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN TÌNH BẠN</t>
+          <t>Chủ đề: Giữ gìn tình bạn</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -983,7 +983,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN TÌNH BẠN</t>
+          <t>Chủ đề: Giữ gìn tình bạn</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN TÌNH BẠN</t>
+          <t>Chủ đề: Giữ gìn tình bạn</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN TÌNH BẠN</t>
+          <t>Chủ đề: Giữ gìn tình bạn</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN TÌNH BẠN</t>
+          <t>Chủ đề: Giữ gìn tình bạn</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN TÌNH BẠN</t>
+          <t>Chủ đề: Giữ gìn tình bạn</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN TÌNH BẠN</t>
+          <t>Chủ đề: Giữ gìn tình bạn</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN TÌNH BẠN</t>
+          <t>Chủ đề: Giữ gìn tình bạn</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN TÌNH BẠN</t>
+          <t>Chủ đề: Giữ gìn tình bạn</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN TÌNH BẠN</t>
+          <t>Chủ đề: Giữ gìn tình bạn</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN TÌNH BẠN</t>
+          <t>Chủ đề: Giữ gìn tình bạn</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIỮ GÌN TÌNH BẠN</t>
+          <t>Chủ đề: Giữ gìn tình bạn</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr"/>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr"/>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr"/>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr"/>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr"/>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr"/>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr"/>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr"/>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr"/>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr"/>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr"/>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr"/>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr"/>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr"/>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr"/>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr"/>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr"/>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr"/>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr"/>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr"/>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr"/>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TÔN SƯ TRỌNG ĐẠO</t>
+          <t>Chủ đề: Tôn sư trọng đạo</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr"/>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: SỐNG AN TOÀN VÀ TỰ CHỦ</t>
+          <t>Chủ đề: Sống an toàn và tự chủ</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr"/>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: SỐNG AN TOÀN VÀ TỰ CHỦ</t>
+          <t>Chủ đề: Sống an toàn và tự chủ</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr"/>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: SỐNG AN TOÀN VÀ TỰ CHỦ</t>
+          <t>Chủ đề: Sống an toàn và tự chủ</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr"/>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: SỐNG AN TOÀN VÀ TỰ CHỦ</t>
+          <t>Chủ đề: Sống an toàn và tự chủ</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr"/>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: SỐNG AN TOÀN VÀ TỰ CHỦ</t>
+          <t>Chủ đề: Sống an toàn và tự chủ</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr"/>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: SỐNG AN TOÀN VÀ TỰ CHỦ</t>
+          <t>Chủ đề: Sống an toàn và tự chủ</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr"/>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: SỐNG AN TOÀN VÀ TỰ CHỦ</t>
+          <t>Chủ đề: Sống an toàn và tự chủ</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: SỐNG AN TOÀN VÀ TỰ CHỦ</t>
+          <t>Chủ đề: Sống an toàn và tự chủ</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: SỐNG AN TOÀN VÀ TỰ CHỦ</t>
+          <t>Chủ đề: Sống an toàn và tự chủ</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr"/>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: SỐNG AN TOÀN VÀ TỰ CHỦ</t>
+          <t>Chủ đề: Sống an toàn và tự chủ</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr"/>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: SỐNG AN TOÀN VÀ TỰ CHỦ</t>
+          <t>Chủ đề: Sống an toàn và tự chủ</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr"/>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: SỐNG AN TOÀN VÀ TỰ CHỦ</t>
+          <t>Chủ đề: Sống an toàn và tự chủ</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr"/>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr"/>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr"/>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr"/>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr"/>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr"/>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr"/>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr"/>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr"/>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr"/>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr"/>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr"/>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr"/>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr"/>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr"/>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr"/>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr"/>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr"/>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr"/>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr"/>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr"/>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr"/>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr"/>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr"/>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr"/>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr"/>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr"/>
@@ -3899,7 +3899,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr"/>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr"/>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr"/>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr"/>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr"/>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr"/>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: THAM GIA HOẠT ĐỘNG XÃ HỘI</t>
+          <t>Chủ đề: Tham gia hoạt động xã hội</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr"/>
